--- a/src/main/resources/Template/Template_role.xlsx
+++ b/src/main/resources/Template/Template_role.xlsx
@@ -10,14 +10,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="acHwxZpf82qBw80UkY3hcI0vtjNj5fRK0dPPjTGtGQM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="78Ifg+eDRdlX3WhfA0ERR8B9e1oODV+ULhJC5RKMtKo="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <r>
       <rPr>
@@ -160,11 +160,8 @@
         <color rgb="FFFFFFFF"/>
         <sz val="11.0"/>
       </rPr>
-      <t>(Chọn các giá trị ở cột B - permissions)</t>
-    </r>
-  </si>
-  <si>
-    <t>ID</t>
+      <t>(Chọn các giá trị ở cột A - permissions)</t>
+    </r>
   </si>
   <si>
     <t>Mã quyền</t>
@@ -230,12 +227,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -477,7 +477,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -493,20 +493,16 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="44.25"/>
-    <col customWidth="1" min="2" max="2" width="35.5"/>
-    <col customWidth="1" min="3" max="3" width="44.88"/>
+    <col customWidth="1" min="1" max="1" width="35.5"/>
+    <col customWidth="1" min="2" max="2" width="44.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="42.0" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Template/Template_role.xlsx
+++ b/src/main/resources/Template/Template_role.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tranp\libraryBE\src\main\resources\Template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA1B3B8-7D67-4965-A84C-FAFC429FCB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Trang tính3" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="permissions" sheetId="2" r:id="rId5"/>
+    <sheet name="Trang tính3" sheetId="1" r:id="rId1"/>
+    <sheet name="permissions" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="78Ifg+eDRdlX3WhfA0ERR8B9e1oODV+ULhJC5RKMtKo="/>
@@ -21,28 +30,28 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">Mã vai trò </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">* 
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <i/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t>(Chỉ được phép nhập ký tự chữ cái, số và dấu ‘_’)</t>
     </r>
@@ -50,28 +59,28 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t>Tên vai trò *</t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve"> 
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <i/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t>(Cho phép nhập freetext)</t>
     </r>
@@ -79,28 +88,28 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <b/>
+        <sz val="11"/>
         <color theme="0"/>
-        <sz val="11.0"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">Mô tả  </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
+        <sz val="11"/>
         <color theme="0"/>
-        <sz val="11.0"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <i/>
+        <sz val="11"/>
         <color theme="0"/>
-        <sz val="11.0"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t>(Cho phép nhập freetext)</t>
     </r>
@@ -108,28 +117,28 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">Trạng thái * </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <i/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t>(0 - Không hoạt động, 1 - hoạt động)</t>
     </r>
@@ -137,28 +146,28 @@
   <si>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">Danh sách quyền * </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <rFont val="Times New Roman"/>
         <i/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Times New Roman"/>
       </rPr>
       <t>(Chọn các giá trị ở cột A - permissions)</t>
     </r>
@@ -173,23 +182,46 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
-    <font>
-      <sz val="10.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -198,7 +230,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -208,7 +240,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -222,42 +260,45 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -447,34 +488,37 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="30.25"/>
-    <col customWidth="1" min="2" max="2" width="37.63"/>
-    <col customWidth="1" min="3" max="3" width="44.5"/>
-    <col customWidth="1" min="4" max="4" width="35.75"/>
-    <col customWidth="1" min="5" max="5" width="53.13"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" customWidth="1"/>
+    <col min="3" max="3" width="44.42578125" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="5" max="5" width="53.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="3" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -482,30 +526,31 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="35.5"/>
-    <col customWidth="1" min="2" max="2" width="44.88"/>
+    <col min="1" max="1" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="44.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42.0" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>